--- a/Pharmacy POS.xlsx
+++ b/Pharmacy POS.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="481">
   <si>
     <t>SKU</t>
   </si>
@@ -39,6 +39,9 @@
   </si>
   <si>
     <t>Unit</t>
+  </si>
+  <si>
+    <t>Current Stock</t>
   </si>
   <si>
     <t>ACE 369</t>
@@ -1485,7 +1488,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1506,6 +1509,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1596,8 +1602,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I258" displayName="Products" name="Products" id="1">
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J258" displayName="Products" name="Products" id="1">
+  <tableColumns count="10">
     <tableColumn name="SKU" id="1"/>
     <tableColumn name="Name" id="2"/>
     <tableColumn name="Generic Name" id="3"/>
@@ -1607,6 +1613,7 @@
     <tableColumn name="Tax Rate" id="7"/>
     <tableColumn name="Reorder Level" id="8"/>
     <tableColumn name="Unit" id="9"/>
+    <tableColumn name="Current Stock" id="10"/>
   </tableColumns>
   <tableStyleInfo name="Sheet1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
@@ -1830,7 +1837,8 @@
     <col customWidth="1" min="7" max="7" width="15.5"/>
     <col customWidth="1" min="8" max="8" width="15.88"/>
     <col customWidth="1" min="9" max="9" width="11.5"/>
-    <col customWidth="1" min="10" max="14" width="8.63"/>
+    <col customWidth="1" min="10" max="10" width="16.0"/>
+    <col customWidth="1" min="11" max="14" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -1861,14 +1869,17 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
@@ -1878,16 +1889,19 @@
       <c r="G2" s="3"/>
       <c r="H2" s="4"/>
       <c r="I2" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J2" s="7">
+        <v>1.0</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4"/>
@@ -1897,16 +1911,19 @@
       <c r="G3" s="3"/>
       <c r="H3" s="4"/>
       <c r="I3" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J3" s="7">
+        <v>2.0</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="4"/>
@@ -1916,16 +1933,19 @@
       <c r="G4" s="3"/>
       <c r="H4" s="4"/>
       <c r="I4" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J4" s="7">
+        <v>3.0</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4"/>
@@ -1935,16 +1955,19 @@
       <c r="G5" s="3"/>
       <c r="H5" s="4"/>
       <c r="I5" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J5" s="7">
+        <v>4.0</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="4"/>
@@ -1954,16 +1977,19 @@
       <c r="G6" s="3"/>
       <c r="H6" s="4"/>
       <c r="I6" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J6" s="7">
+        <v>5.0</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="4"/>
@@ -1973,16 +1999,19 @@
       <c r="G7" s="3"/>
       <c r="H7" s="4"/>
       <c r="I7" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J7" s="7">
+        <v>6.0</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="4"/>
@@ -1992,16 +2021,19 @@
       <c r="G8" s="3"/>
       <c r="H8" s="4"/>
       <c r="I8" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J8" s="7">
+        <v>7.0</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="4"/>
@@ -2011,16 +2043,19 @@
       <c r="G9" s="3"/>
       <c r="H9" s="4"/>
       <c r="I9" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J9" s="7">
+        <v>8.0</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="3"/>
       <c r="B10" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="4"/>
@@ -2030,16 +2065,19 @@
       <c r="G10" s="3"/>
       <c r="H10" s="4"/>
       <c r="I10" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J10" s="7">
+        <v>9.0</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="3"/>
       <c r="B11" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="4"/>
@@ -2049,16 +2087,19 @@
       <c r="G11" s="3"/>
       <c r="H11" s="4"/>
       <c r="I11" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J11" s="7">
+        <v>10.0</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="3"/>
       <c r="B12" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="4"/>
@@ -2068,16 +2109,19 @@
       <c r="G12" s="3"/>
       <c r="H12" s="4"/>
       <c r="I12" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J12" s="7">
+        <v>11.0</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="3"/>
       <c r="B13" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="4"/>
@@ -2087,16 +2131,19 @@
       <c r="G13" s="3"/>
       <c r="H13" s="4"/>
       <c r="I13" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J13" s="7">
+        <v>12.0</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="3"/>
       <c r="B14" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="4"/>
@@ -2106,16 +2153,19 @@
       <c r="G14" s="3"/>
       <c r="H14" s="4"/>
       <c r="I14" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J14" s="7">
+        <v>13.0</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="3"/>
       <c r="B15" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="4"/>
@@ -2125,16 +2175,19 @@
       <c r="G15" s="3"/>
       <c r="H15" s="4"/>
       <c r="I15" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J15" s="7">
+        <v>14.0</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="3"/>
       <c r="B16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="4"/>
@@ -2144,16 +2197,19 @@
       <c r="G16" s="3"/>
       <c r="H16" s="4"/>
       <c r="I16" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J16" s="7">
+        <v>15.0</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="3"/>
       <c r="B17" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="4"/>
@@ -2163,16 +2219,19 @@
       <c r="G17" s="3"/>
       <c r="H17" s="4"/>
       <c r="I17" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J17" s="7">
+        <v>16.0</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="3"/>
       <c r="B18" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="4"/>
@@ -2182,16 +2241,19 @@
       <c r="G18" s="3"/>
       <c r="H18" s="4"/>
       <c r="I18" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J18" s="7">
+        <v>17.0</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="3"/>
       <c r="B19" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="4"/>
@@ -2201,16 +2263,19 @@
       <c r="G19" s="3"/>
       <c r="H19" s="4"/>
       <c r="I19" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J19" s="7">
+        <v>18.0</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="3"/>
       <c r="B20" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="4"/>
@@ -2220,16 +2285,19 @@
       <c r="G20" s="3"/>
       <c r="H20" s="4"/>
       <c r="I20" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J20" s="7">
+        <v>19.0</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="3"/>
       <c r="B21" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="4"/>
@@ -2239,16 +2307,19 @@
       <c r="G21" s="3"/>
       <c r="H21" s="4"/>
       <c r="I21" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J21" s="7">
+        <v>20.0</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="3"/>
       <c r="B22" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="4"/>
@@ -2258,16 +2329,19 @@
       <c r="G22" s="3"/>
       <c r="H22" s="4"/>
       <c r="I22" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J22" s="7">
+        <v>21.0</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="3"/>
       <c r="B23" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4"/>
@@ -2277,16 +2351,19 @@
       <c r="G23" s="3"/>
       <c r="H23" s="4"/>
       <c r="I23" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J23" s="7">
+        <v>22.0</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="3"/>
       <c r="B24" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="4"/>
@@ -2296,16 +2373,19 @@
       <c r="G24" s="3"/>
       <c r="H24" s="4"/>
       <c r="I24" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="J24" s="7">
+        <v>23.0</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="3"/>
       <c r="B25" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="4"/>
@@ -2315,16 +2395,19 @@
       <c r="G25" s="3"/>
       <c r="H25" s="4"/>
       <c r="I25" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J25" s="7">
+        <v>24.0</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="3"/>
       <c r="B26" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="4"/>
@@ -2334,16 +2417,19 @@
       <c r="G26" s="3"/>
       <c r="H26" s="4"/>
       <c r="I26" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J26" s="7">
+        <v>25.0</v>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="3"/>
       <c r="B27" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="4"/>
@@ -2353,16 +2439,19 @@
       <c r="G27" s="3"/>
       <c r="H27" s="4"/>
       <c r="I27" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J27" s="7">
+        <v>26.0</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="3"/>
       <c r="B28" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="4"/>
@@ -2372,16 +2461,19 @@
       <c r="G28" s="3"/>
       <c r="H28" s="4"/>
       <c r="I28" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J28" s="7">
+        <v>27.0</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="3"/>
       <c r="B29" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="4"/>
@@ -2391,16 +2483,19 @@
       <c r="G29" s="3"/>
       <c r="H29" s="4"/>
       <c r="I29" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J29" s="7">
+        <v>28.0</v>
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="4"/>
@@ -2410,16 +2505,19 @@
       <c r="G30" s="3"/>
       <c r="H30" s="4"/>
       <c r="I30" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J30" s="7">
+        <v>29.0</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="3"/>
       <c r="B31" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="4"/>
@@ -2429,16 +2527,19 @@
       <c r="G31" s="3"/>
       <c r="H31" s="4"/>
       <c r="I31" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J31" s="7">
+        <v>30.0</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="3"/>
       <c r="B32" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="4"/>
@@ -2448,16 +2549,19 @@
       <c r="G32" s="3"/>
       <c r="H32" s="4"/>
       <c r="I32" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J32" s="7">
+        <v>31.0</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="3"/>
       <c r="B33" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="4"/>
@@ -2467,16 +2571,19 @@
       <c r="G33" s="3"/>
       <c r="H33" s="4"/>
       <c r="I33" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J33" s="7">
+        <v>32.0</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="3"/>
       <c r="B34" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="4"/>
@@ -2486,16 +2593,19 @@
       <c r="G34" s="3"/>
       <c r="H34" s="4"/>
       <c r="I34" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J34" s="7">
+        <v>33.0</v>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="3"/>
       <c r="B35" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="4"/>
@@ -2505,16 +2615,19 @@
       <c r="G35" s="3"/>
       <c r="H35" s="4"/>
       <c r="I35" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J35" s="7">
+        <v>34.0</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="3"/>
       <c r="B36" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="4"/>
@@ -2524,16 +2637,19 @@
       <c r="G36" s="3"/>
       <c r="H36" s="4"/>
       <c r="I36" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J36" s="7">
+        <v>35.0</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="3"/>
       <c r="B37" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>76</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="4"/>
@@ -2543,16 +2659,19 @@
       <c r="G37" s="3"/>
       <c r="H37" s="4"/>
       <c r="I37" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J37" s="7">
+        <v>36.0</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="3"/>
       <c r="B38" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="4"/>
@@ -2562,16 +2681,19 @@
       <c r="G38" s="3"/>
       <c r="H38" s="4"/>
       <c r="I38" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J38" s="7">
+        <v>37.0</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="3"/>
       <c r="B39" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>79</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="4"/>
@@ -2581,16 +2703,19 @@
       <c r="G39" s="3"/>
       <c r="H39" s="4"/>
       <c r="I39" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J39" s="7">
+        <v>38.0</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="3"/>
       <c r="B40" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="4"/>
@@ -2600,16 +2725,19 @@
       <c r="G40" s="3"/>
       <c r="H40" s="4"/>
       <c r="I40" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J40" s="7">
+        <v>39.0</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="3"/>
       <c r="B41" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="4"/>
@@ -2619,16 +2747,19 @@
       <c r="G41" s="3"/>
       <c r="H41" s="4"/>
       <c r="I41" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J41" s="7">
+        <v>40.0</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="3"/>
       <c r="B42" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="4"/>
@@ -2638,16 +2769,19 @@
       <c r="G42" s="3"/>
       <c r="H42" s="4"/>
       <c r="I42" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J42" s="7">
+        <v>41.0</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="3"/>
       <c r="B43" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="4"/>
@@ -2657,16 +2791,19 @@
       <c r="G43" s="3"/>
       <c r="H43" s="4"/>
       <c r="I43" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J43" s="7">
+        <v>42.0</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="3"/>
       <c r="B44" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="4"/>
@@ -2676,16 +2813,19 @@
       <c r="G44" s="3"/>
       <c r="H44" s="4"/>
       <c r="I44" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J44" s="7">
+        <v>43.0</v>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="3"/>
       <c r="B45" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="4"/>
@@ -2695,16 +2835,19 @@
       <c r="G45" s="3"/>
       <c r="H45" s="4"/>
       <c r="I45" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J45" s="7">
+        <v>44.0</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="3"/>
       <c r="B46" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="4"/>
@@ -2714,16 +2857,19 @@
       <c r="G46" s="3"/>
       <c r="H46" s="4"/>
       <c r="I46" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J46" s="7">
+        <v>45.0</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="3"/>
       <c r="B47" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="4"/>
@@ -2733,16 +2879,19 @@
       <c r="G47" s="3"/>
       <c r="H47" s="4"/>
       <c r="I47" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="J47" s="7">
+        <v>46.0</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="3"/>
       <c r="B48" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="4"/>
@@ -2752,16 +2901,19 @@
       <c r="G48" s="3"/>
       <c r="H48" s="4"/>
       <c r="I48" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J48" s="7">
+        <v>47.0</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="3"/>
       <c r="B49" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="4"/>
@@ -2771,16 +2923,19 @@
       <c r="G49" s="3"/>
       <c r="H49" s="4"/>
       <c r="I49" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J49" s="7">
+        <v>48.0</v>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="3"/>
       <c r="B50" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="D50" s="3"/>
       <c r="E50" s="4"/>
@@ -2790,16 +2945,19 @@
       <c r="G50" s="3"/>
       <c r="H50" s="4"/>
       <c r="I50" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J50" s="7">
+        <v>49.0</v>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="3"/>
       <c r="B51" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="4"/>
@@ -2809,16 +2967,19 @@
       <c r="G51" s="3"/>
       <c r="H51" s="4"/>
       <c r="I51" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J51" s="7">
+        <v>50.0</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="3"/>
       <c r="B52" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="4"/>
@@ -2828,16 +2989,19 @@
       <c r="G52" s="3"/>
       <c r="H52" s="4"/>
       <c r="I52" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J52" s="7">
+        <v>51.0</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="3"/>
       <c r="B53" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="4"/>
@@ -2847,16 +3011,19 @@
       <c r="G53" s="3"/>
       <c r="H53" s="4"/>
       <c r="I53" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J53" s="7">
+        <v>52.0</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="3"/>
       <c r="B54" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D54" s="3"/>
       <c r="E54" s="4"/>
@@ -2866,16 +3033,19 @@
       <c r="G54" s="3"/>
       <c r="H54" s="4"/>
       <c r="I54" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J54" s="7">
+        <v>53.0</v>
       </c>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="3"/>
       <c r="B55" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="4"/>
@@ -2885,16 +3055,19 @@
       <c r="G55" s="3"/>
       <c r="H55" s="4"/>
       <c r="I55" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J55" s="7">
+        <v>54.0</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="3"/>
       <c r="B56" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="4"/>
@@ -2904,16 +3077,19 @@
       <c r="G56" s="3"/>
       <c r="H56" s="4"/>
       <c r="I56" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J56" s="7">
+        <v>55.0</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="3"/>
       <c r="B57" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D57" s="3"/>
       <c r="E57" s="4"/>
@@ -2923,16 +3099,19 @@
       <c r="G57" s="3"/>
       <c r="H57" s="4"/>
       <c r="I57" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J57" s="7">
+        <v>56.0</v>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="3"/>
       <c r="B58" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D58" s="3"/>
       <c r="E58" s="4"/>
@@ -2942,16 +3121,19 @@
       <c r="G58" s="3"/>
       <c r="H58" s="4"/>
       <c r="I58" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J58" s="7">
+        <v>57.0</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="3"/>
       <c r="B59" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D59" s="3"/>
       <c r="E59" s="4"/>
@@ -2961,16 +3143,19 @@
       <c r="G59" s="3"/>
       <c r="H59" s="4"/>
       <c r="I59" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="J59" s="7">
+        <v>58.0</v>
       </c>
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="3"/>
       <c r="B60" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D60" s="3"/>
       <c r="E60" s="4"/>
@@ -2980,16 +3165,19 @@
       <c r="G60" s="3"/>
       <c r="H60" s="4"/>
       <c r="I60" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J60" s="7">
+        <v>59.0</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="3"/>
       <c r="B61" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D61" s="3"/>
       <c r="E61" s="4"/>
@@ -2999,16 +3187,19 @@
       <c r="G61" s="3"/>
       <c r="H61" s="4"/>
       <c r="I61" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="J61" s="7">
+        <v>60.0</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="3"/>
       <c r="B62" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D62" s="3"/>
       <c r="E62" s="4"/>
@@ -3018,16 +3209,19 @@
       <c r="G62" s="3"/>
       <c r="H62" s="4"/>
       <c r="I62" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="J62" s="7">
+        <v>61.0</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="3"/>
       <c r="B63" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="4"/>
@@ -3037,16 +3231,19 @@
       <c r="G63" s="3"/>
       <c r="H63" s="4"/>
       <c r="I63" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J63" s="7">
+        <v>62.0</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="3"/>
       <c r="B64" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="4"/>
@@ -3056,16 +3253,19 @@
       <c r="G64" s="3"/>
       <c r="H64" s="4"/>
       <c r="I64" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J64" s="7">
+        <v>63.0</v>
       </c>
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="3"/>
       <c r="B65" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D65" s="3"/>
       <c r="E65" s="4"/>
@@ -3075,16 +3275,19 @@
       <c r="G65" s="3"/>
       <c r="H65" s="4"/>
       <c r="I65" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J65" s="7">
+        <v>64.0</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="3"/>
       <c r="B66" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D66" s="3"/>
       <c r="E66" s="4"/>
@@ -3094,16 +3297,19 @@
       <c r="G66" s="3"/>
       <c r="H66" s="4"/>
       <c r="I66" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J66" s="7">
+        <v>65.0</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="3"/>
       <c r="B67" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="4"/>
@@ -3113,16 +3319,19 @@
       <c r="G67" s="3"/>
       <c r="H67" s="4"/>
       <c r="I67" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J67" s="7">
+        <v>66.0</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="3"/>
       <c r="B68" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="4"/>
@@ -3132,16 +3341,19 @@
       <c r="G68" s="3"/>
       <c r="H68" s="4"/>
       <c r="I68" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J68" s="7">
+        <v>67.0</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="3"/>
       <c r="B69" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="4"/>
@@ -3151,16 +3363,19 @@
       <c r="G69" s="3"/>
       <c r="H69" s="4"/>
       <c r="I69" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J69" s="7">
+        <v>68.0</v>
       </c>
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="3"/>
       <c r="B70" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D70" s="3"/>
       <c r="E70" s="4"/>
@@ -3170,16 +3385,19 @@
       <c r="G70" s="3"/>
       <c r="H70" s="4"/>
       <c r="I70" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J70" s="7">
+        <v>69.0</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="3"/>
       <c r="B71" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D71" s="3"/>
       <c r="E71" s="4"/>
@@ -3189,16 +3407,19 @@
       <c r="G71" s="3"/>
       <c r="H71" s="4"/>
       <c r="I71" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="J71" s="7">
+        <v>70.0</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="3"/>
       <c r="B72" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="4"/>
@@ -3208,16 +3429,19 @@
       <c r="G72" s="3"/>
       <c r="H72" s="4"/>
       <c r="I72" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J72" s="7">
+        <v>71.0</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="3"/>
       <c r="B73" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D73" s="3"/>
       <c r="E73" s="4"/>
@@ -3227,16 +3451,19 @@
       <c r="G73" s="3"/>
       <c r="H73" s="4"/>
       <c r="I73" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J73" s="7">
+        <v>72.0</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="3"/>
       <c r="B74" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D74" s="3"/>
       <c r="E74" s="4"/>
@@ -3246,16 +3473,19 @@
       <c r="G74" s="3"/>
       <c r="H74" s="4"/>
       <c r="I74" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J74" s="7">
+        <v>73.0</v>
       </c>
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="3"/>
       <c r="B75" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D75" s="3"/>
       <c r="E75" s="4"/>
@@ -3265,16 +3495,19 @@
       <c r="G75" s="3"/>
       <c r="H75" s="4"/>
       <c r="I75" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J75" s="7">
+        <v>74.0</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="3"/>
       <c r="B76" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D76" s="3"/>
       <c r="E76" s="4"/>
@@ -3284,16 +3517,19 @@
       <c r="G76" s="3"/>
       <c r="H76" s="4"/>
       <c r="I76" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J76" s="7">
+        <v>75.0</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="3"/>
       <c r="B77" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="4"/>
@@ -3303,16 +3539,19 @@
       <c r="G77" s="3"/>
       <c r="H77" s="4"/>
       <c r="I77" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J77" s="7">
+        <v>76.0</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="3"/>
       <c r="B78" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D78" s="3"/>
       <c r="E78" s="4"/>
@@ -3322,16 +3561,19 @@
       <c r="G78" s="3"/>
       <c r="H78" s="4"/>
       <c r="I78" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J78" s="7">
+        <v>77.0</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="3"/>
       <c r="B79" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="4"/>
@@ -3341,16 +3583,19 @@
       <c r="G79" s="3"/>
       <c r="H79" s="4"/>
       <c r="I79" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J79" s="7">
+        <v>78.0</v>
       </c>
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="3"/>
       <c r="B80" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D80" s="3"/>
       <c r="E80" s="4"/>
@@ -3360,16 +3605,19 @@
       <c r="G80" s="3"/>
       <c r="H80" s="4"/>
       <c r="I80" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J80" s="7">
+        <v>79.0</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="3"/>
       <c r="B81" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C81" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>157</v>
       </c>
       <c r="D81" s="3"/>
       <c r="E81" s="4"/>
@@ -3379,16 +3627,19 @@
       <c r="G81" s="3"/>
       <c r="H81" s="4"/>
       <c r="I81" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J81" s="7">
+        <v>80.0</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="3"/>
       <c r="B82" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D82" s="3"/>
       <c r="E82" s="4"/>
@@ -3398,16 +3649,19 @@
       <c r="G82" s="3"/>
       <c r="H82" s="4"/>
       <c r="I82" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J82" s="7">
+        <v>81.0</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="3"/>
       <c r="B83" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="4"/>
@@ -3417,16 +3671,19 @@
       <c r="G83" s="3"/>
       <c r="H83" s="4"/>
       <c r="I83" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J83" s="7">
+        <v>82.0</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="3"/>
       <c r="B84" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D84" s="3"/>
       <c r="E84" s="4"/>
@@ -3436,16 +3693,19 @@
       <c r="G84" s="3"/>
       <c r="H84" s="4"/>
       <c r="I84" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J84" s="7">
+        <v>83.0</v>
       </c>
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="3"/>
       <c r="B85" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D85" s="3"/>
       <c r="E85" s="4"/>
@@ -3455,16 +3715,19 @@
       <c r="G85" s="3"/>
       <c r="H85" s="4"/>
       <c r="I85" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J85" s="7">
+        <v>84.0</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="3"/>
       <c r="B86" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D86" s="3"/>
       <c r="E86" s="4"/>
@@ -3474,16 +3737,19 @@
       <c r="G86" s="3"/>
       <c r="H86" s="4"/>
       <c r="I86" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J86" s="7">
+        <v>85.0</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="3"/>
       <c r="B87" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D87" s="3"/>
       <c r="E87" s="4"/>
@@ -3493,16 +3759,19 @@
       <c r="G87" s="3"/>
       <c r="H87" s="4"/>
       <c r="I87" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="J87" s="7">
+        <v>86.0</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="3"/>
       <c r="B88" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D88" s="3"/>
       <c r="E88" s="4"/>
@@ -3512,16 +3781,19 @@
       <c r="G88" s="3"/>
       <c r="H88" s="4"/>
       <c r="I88" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J88" s="7">
+        <v>87.0</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
       <c r="A89" s="3"/>
       <c r="B89" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D89" s="3"/>
       <c r="E89" s="4"/>
@@ -3531,16 +3803,19 @@
       <c r="G89" s="3"/>
       <c r="H89" s="4"/>
       <c r="I89" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J89" s="7">
+        <v>88.0</v>
       </c>
     </row>
     <row r="90" ht="14.25" customHeight="1">
       <c r="A90" s="3"/>
       <c r="B90" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D90" s="3"/>
       <c r="E90" s="4"/>
@@ -3550,16 +3825,19 @@
       <c r="G90" s="3"/>
       <c r="H90" s="4"/>
       <c r="I90" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J90" s="7">
+        <v>89.0</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c r="A91" s="3"/>
       <c r="B91" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D91" s="3"/>
       <c r="E91" s="4"/>
@@ -3569,16 +3847,19 @@
       <c r="G91" s="3"/>
       <c r="H91" s="4"/>
       <c r="I91" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J91" s="7">
+        <v>90.0</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
       <c r="A92" s="3"/>
       <c r="B92" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D92" s="3"/>
       <c r="E92" s="4"/>
@@ -3588,16 +3869,19 @@
       <c r="G92" s="3"/>
       <c r="H92" s="4"/>
       <c r="I92" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="J92" s="7">
+        <v>91.0</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c r="A93" s="3"/>
       <c r="B93" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="4"/>
@@ -3607,16 +3891,19 @@
       <c r="G93" s="3"/>
       <c r="H93" s="4"/>
       <c r="I93" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="J93" s="7">
+        <v>92.0</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c r="A94" s="3"/>
       <c r="B94" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>176</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="4"/>
@@ -3626,16 +3913,19 @@
       <c r="G94" s="3"/>
       <c r="H94" s="4"/>
       <c r="I94" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="J94" s="7">
+        <v>93.0</v>
       </c>
     </row>
     <row r="95" ht="14.25" customHeight="1">
       <c r="A95" s="3"/>
       <c r="B95" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D95" s="3"/>
       <c r="E95" s="4"/>
@@ -3645,16 +3935,19 @@
       <c r="G95" s="3"/>
       <c r="H95" s="4"/>
       <c r="I95" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J95" s="7">
+        <v>94.0</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
       <c r="A96" s="3"/>
       <c r="B96" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="4"/>
@@ -3664,16 +3957,19 @@
       <c r="G96" s="3"/>
       <c r="H96" s="4"/>
       <c r="I96" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J96" s="7">
+        <v>95.0</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
       <c r="A97" s="3"/>
       <c r="B97" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C97" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>181</v>
       </c>
       <c r="D97" s="3"/>
       <c r="E97" s="4"/>
@@ -3683,16 +3979,19 @@
       <c r="G97" s="3"/>
       <c r="H97" s="4"/>
       <c r="I97" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J97" s="7">
+        <v>96.0</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D98" s="3"/>
       <c r="E98" s="4"/>
@@ -3702,16 +4001,19 @@
       <c r="G98" s="3"/>
       <c r="H98" s="4"/>
       <c r="I98" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
+      </c>
+      <c r="J98" s="7">
+        <v>97.0</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D99" s="3"/>
       <c r="E99" s="4"/>
@@ -3721,16 +4023,19 @@
       <c r="G99" s="3"/>
       <c r="H99" s="4"/>
       <c r="I99" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J99" s="7">
+        <v>98.0</v>
       </c>
     </row>
     <row r="100" ht="14.25" customHeight="1">
       <c r="A100" s="3"/>
       <c r="B100" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D100" s="3"/>
       <c r="E100" s="4"/>
@@ -3740,16 +4045,19 @@
       <c r="G100" s="3"/>
       <c r="H100" s="4"/>
       <c r="I100" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J100" s="7">
+        <v>99.0</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
       <c r="A101" s="3"/>
       <c r="B101" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D101" s="3"/>
       <c r="E101" s="4"/>
@@ -3759,16 +4067,19 @@
       <c r="G101" s="3"/>
       <c r="H101" s="4"/>
       <c r="I101" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
+      </c>
+      <c r="J101" s="7">
+        <v>100.0</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
       <c r="A102" s="3"/>
       <c r="B102" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D102" s="3"/>
       <c r="E102" s="4"/>
@@ -3778,16 +4089,19 @@
       <c r="G102" s="3"/>
       <c r="H102" s="4"/>
       <c r="I102" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J102" s="7">
+        <v>101.0</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
       <c r="A103" s="3"/>
       <c r="B103" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D103" s="3"/>
       <c r="E103" s="4"/>
@@ -3797,16 +4111,19 @@
       <c r="G103" s="3"/>
       <c r="H103" s="4"/>
       <c r="I103" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J103" s="7">
+        <v>102.0</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
       <c r="A104" s="3"/>
       <c r="B104" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D104" s="3"/>
       <c r="E104" s="4"/>
@@ -3816,16 +4133,19 @@
       <c r="G104" s="3"/>
       <c r="H104" s="4"/>
       <c r="I104" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J104" s="7">
+        <v>103.0</v>
       </c>
     </row>
     <row r="105" ht="14.25" customHeight="1">
       <c r="A105" s="3"/>
       <c r="B105" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D105" s="3"/>
       <c r="E105" s="4"/>
@@ -3835,16 +4155,19 @@
       <c r="G105" s="3"/>
       <c r="H105" s="4"/>
       <c r="I105" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J105" s="7">
+        <v>104.0</v>
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
       <c r="A106" s="3"/>
       <c r="B106" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D106" s="3"/>
       <c r="E106" s="4"/>
@@ -3854,16 +4177,19 @@
       <c r="G106" s="3"/>
       <c r="H106" s="4"/>
       <c r="I106" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J106" s="7">
+        <v>105.0</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
       <c r="A107" s="3"/>
       <c r="B107" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D107" s="3"/>
       <c r="E107" s="4"/>
@@ -3873,16 +4199,19 @@
       <c r="G107" s="3"/>
       <c r="H107" s="4"/>
       <c r="I107" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J107" s="7">
+        <v>106.0</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
       <c r="A108" s="3"/>
       <c r="B108" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="4"/>
@@ -3892,16 +4221,19 @@
       <c r="G108" s="3"/>
       <c r="H108" s="4"/>
       <c r="I108" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J108" s="7">
+        <v>107.0</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
       <c r="A109" s="3"/>
       <c r="B109" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C109" s="4" t="s">
         <v>206</v>
-      </c>
-      <c r="C109" s="4" t="s">
-        <v>205</v>
       </c>
       <c r="D109" s="3"/>
       <c r="E109" s="4"/>
@@ -3911,16 +4243,19 @@
       <c r="G109" s="3"/>
       <c r="H109" s="4"/>
       <c r="I109" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J109" s="7">
+        <v>108.0</v>
       </c>
     </row>
     <row r="110" ht="14.25" customHeight="1">
       <c r="A110" s="3"/>
       <c r="B110" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D110" s="3"/>
       <c r="E110" s="4"/>
@@ -3930,16 +4265,19 @@
       <c r="G110" s="3"/>
       <c r="H110" s="4"/>
       <c r="I110" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J110" s="7">
+        <v>109.0</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
       <c r="A111" s="3"/>
       <c r="B111" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C111" s="4" t="s">
         <v>209</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>208</v>
       </c>
       <c r="D111" s="3"/>
       <c r="E111" s="4"/>
@@ -3949,16 +4287,19 @@
       <c r="G111" s="3"/>
       <c r="H111" s="4"/>
       <c r="I111" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J111" s="7">
+        <v>110.0</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
       <c r="A112" s="3"/>
       <c r="B112" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D112" s="3"/>
       <c r="E112" s="4"/>
@@ -3968,16 +4309,19 @@
       <c r="G112" s="3"/>
       <c r="H112" s="4"/>
       <c r="I112" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J112" s="7">
+        <v>111.0</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
       <c r="A113" s="3"/>
       <c r="B113" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D113" s="3"/>
       <c r="E113" s="4"/>
@@ -3987,16 +4331,19 @@
       <c r="G113" s="3"/>
       <c r="H113" s="4"/>
       <c r="I113" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J113" s="7">
+        <v>112.0</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
       <c r="A114" s="3"/>
       <c r="B114" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D114" s="3"/>
       <c r="E114" s="4"/>
@@ -4006,16 +4353,19 @@
       <c r="G114" s="3"/>
       <c r="H114" s="4"/>
       <c r="I114" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J114" s="7">
+        <v>113.0</v>
       </c>
     </row>
     <row r="115" ht="14.25" customHeight="1">
       <c r="A115" s="3"/>
       <c r="B115" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D115" s="3"/>
       <c r="E115" s="4"/>
@@ -4025,16 +4375,19 @@
       <c r="G115" s="3"/>
       <c r="H115" s="4"/>
       <c r="I115" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J115" s="7">
+        <v>114.0</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
       <c r="A116" s="3"/>
       <c r="B116" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C116" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>216</v>
       </c>
       <c r="D116" s="3"/>
       <c r="E116" s="4"/>
@@ -4044,16 +4397,19 @@
       <c r="G116" s="3"/>
       <c r="H116" s="4"/>
       <c r="I116" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J116" s="7">
+        <v>115.0</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
       <c r="A117" s="3"/>
       <c r="B117" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D117" s="3"/>
       <c r="E117" s="4"/>
@@ -4063,16 +4419,19 @@
       <c r="G117" s="3"/>
       <c r="H117" s="4"/>
       <c r="I117" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J117" s="7">
+        <v>116.0</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
       <c r="A118" s="3"/>
       <c r="B118" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D118" s="3"/>
       <c r="E118" s="4"/>
@@ -4082,16 +4441,19 @@
       <c r="G118" s="3"/>
       <c r="H118" s="4"/>
       <c r="I118" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J118" s="7">
+        <v>117.0</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
       <c r="A119" s="3"/>
       <c r="B119" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D119" s="3"/>
       <c r="E119" s="4"/>
@@ -4101,16 +4463,19 @@
       <c r="G119" s="3"/>
       <c r="H119" s="4"/>
       <c r="I119" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J119" s="7">
+        <v>118.0</v>
       </c>
     </row>
     <row r="120" ht="14.25" customHeight="1">
       <c r="A120" s="3"/>
       <c r="B120" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D120" s="3"/>
       <c r="E120" s="4"/>
@@ -4120,16 +4485,19 @@
       <c r="G120" s="3"/>
       <c r="H120" s="4"/>
       <c r="I120" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J120" s="7">
+        <v>119.0</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
       <c r="A121" s="3"/>
       <c r="B121" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D121" s="3"/>
       <c r="E121" s="4"/>
@@ -4139,16 +4507,19 @@
       <c r="G121" s="3"/>
       <c r="H121" s="4"/>
       <c r="I121" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J121" s="7">
+        <v>120.0</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
       <c r="A122" s="3"/>
       <c r="B122" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D122" s="3"/>
       <c r="E122" s="4"/>
@@ -4156,16 +4527,19 @@
       <c r="G122" s="3"/>
       <c r="H122" s="4"/>
       <c r="I122" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J122" s="7">
+        <v>121.0</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
       <c r="A123" s="3"/>
       <c r="B123" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D123" s="3"/>
       <c r="E123" s="4"/>
@@ -4175,16 +4549,19 @@
       <c r="G123" s="3"/>
       <c r="H123" s="4"/>
       <c r="I123" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J123" s="7">
+        <v>122.0</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
       <c r="A124" s="3"/>
       <c r="B124" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D124" s="3"/>
       <c r="E124" s="4"/>
@@ -4194,16 +4571,19 @@
       <c r="G124" s="3"/>
       <c r="H124" s="4"/>
       <c r="I124" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J124" s="7">
+        <v>123.0</v>
       </c>
     </row>
     <row r="125" ht="14.25" customHeight="1">
       <c r="A125" s="3"/>
       <c r="B125" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D125" s="3"/>
       <c r="E125" s="4"/>
@@ -4213,16 +4593,19 @@
       <c r="G125" s="3"/>
       <c r="H125" s="4"/>
       <c r="I125" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J125" s="7">
+        <v>124.0</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
       <c r="A126" s="3"/>
       <c r="B126" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C126" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>230</v>
       </c>
       <c r="D126" s="3"/>
       <c r="E126" s="4"/>
@@ -4232,16 +4615,19 @@
       <c r="G126" s="3"/>
       <c r="H126" s="4"/>
       <c r="I126" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J126" s="7">
+        <v>125.0</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
       <c r="A127" s="3"/>
       <c r="B127" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D127" s="3"/>
       <c r="E127" s="4"/>
@@ -4251,16 +4637,19 @@
       <c r="G127" s="3"/>
       <c r="H127" s="4"/>
       <c r="I127" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J127" s="7">
+        <v>126.0</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
       <c r="A128" s="3"/>
       <c r="B128" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D128" s="3"/>
       <c r="E128" s="4"/>
@@ -4270,16 +4659,19 @@
       <c r="G128" s="3"/>
       <c r="H128" s="4"/>
       <c r="I128" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J128" s="7">
+        <v>127.0</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
       <c r="A129" s="3"/>
       <c r="B129" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D129" s="3"/>
       <c r="E129" s="4"/>
@@ -4289,16 +4681,19 @@
       <c r="G129" s="3"/>
       <c r="H129" s="4"/>
       <c r="I129" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
+      </c>
+      <c r="J129" s="7">
+        <v>128.0</v>
       </c>
     </row>
     <row r="130" ht="14.25" customHeight="1">
       <c r="A130" s="3"/>
       <c r="B130" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D130" s="3"/>
       <c r="E130" s="4"/>
@@ -4308,16 +4703,19 @@
       <c r="G130" s="3"/>
       <c r="H130" s="4"/>
       <c r="I130" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
+      </c>
+      <c r="J130" s="7">
+        <v>129.0</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
       <c r="A131" s="3"/>
       <c r="B131" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D131" s="3"/>
       <c r="E131" s="4"/>
@@ -4327,16 +4725,19 @@
       <c r="G131" s="3"/>
       <c r="H131" s="4"/>
       <c r="I131" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J131" s="7">
+        <v>130.0</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
       <c r="A132" s="3"/>
       <c r="B132" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D132" s="3"/>
       <c r="E132" s="4"/>
@@ -4346,16 +4747,19 @@
       <c r="G132" s="3"/>
       <c r="H132" s="4"/>
       <c r="I132" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J132" s="7">
+        <v>131.0</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
       <c r="A133" s="3"/>
       <c r="B133" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D133" s="3"/>
       <c r="E133" s="4"/>
@@ -4365,16 +4769,19 @@
       <c r="G133" s="3"/>
       <c r="H133" s="4"/>
       <c r="I133" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J133" s="7">
+        <v>132.0</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
       <c r="A134" s="3"/>
       <c r="B134" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D134" s="3"/>
       <c r="E134" s="4"/>
@@ -4384,16 +4791,19 @@
       <c r="G134" s="3"/>
       <c r="H134" s="4"/>
       <c r="I134" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J134" s="7">
+        <v>133.0</v>
       </c>
     </row>
     <row r="135" ht="14.25" customHeight="1">
       <c r="A135" s="3"/>
       <c r="B135" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D135" s="3"/>
       <c r="E135" s="4"/>
@@ -4403,16 +4813,19 @@
       <c r="G135" s="3"/>
       <c r="H135" s="4"/>
       <c r="I135" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J135" s="7">
+        <v>134.0</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
       <c r="A136" s="3"/>
       <c r="B136" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D136" s="3"/>
       <c r="E136" s="4"/>
@@ -4422,16 +4835,19 @@
       <c r="G136" s="3"/>
       <c r="H136" s="4"/>
       <c r="I136" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J136" s="7">
+        <v>135.0</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
       <c r="A137" s="3"/>
       <c r="B137" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C137" s="4" t="s">
         <v>252</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>251</v>
       </c>
       <c r="D137" s="3"/>
       <c r="E137" s="4"/>
@@ -4441,16 +4857,19 @@
       <c r="G137" s="3"/>
       <c r="H137" s="4"/>
       <c r="I137" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J137" s="7">
+        <v>136.0</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
       <c r="A138" s="3"/>
       <c r="B138" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D138" s="3"/>
       <c r="E138" s="4"/>
@@ -4460,16 +4879,19 @@
       <c r="G138" s="3"/>
       <c r="H138" s="4"/>
       <c r="I138" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J138" s="7">
+        <v>137.0</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
       <c r="A139" s="3"/>
       <c r="B139" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D139" s="3"/>
       <c r="E139" s="4"/>
@@ -4479,16 +4901,19 @@
       <c r="G139" s="3"/>
       <c r="H139" s="4"/>
       <c r="I139" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J139" s="7">
+        <v>138.0</v>
       </c>
     </row>
     <row r="140" ht="14.25" customHeight="1">
       <c r="A140" s="3"/>
       <c r="B140" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D140" s="3"/>
       <c r="E140" s="4"/>
@@ -4498,16 +4923,19 @@
       <c r="G140" s="3"/>
       <c r="H140" s="4"/>
       <c r="I140" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J140" s="7">
+        <v>139.0</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
       <c r="A141" s="3"/>
       <c r="B141" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D141" s="3"/>
       <c r="E141" s="4"/>
@@ -4517,16 +4945,19 @@
       <c r="G141" s="3"/>
       <c r="H141" s="4"/>
       <c r="I141" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J141" s="7">
+        <v>140.0</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
       <c r="A142" s="3"/>
       <c r="B142" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D142" s="3"/>
       <c r="E142" s="4"/>
@@ -4536,16 +4967,19 @@
       <c r="G142" s="3"/>
       <c r="H142" s="4"/>
       <c r="I142" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
+      </c>
+      <c r="J142" s="7">
+        <v>141.0</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
       <c r="A143" s="3"/>
       <c r="B143" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D143" s="3"/>
       <c r="E143" s="4"/>
@@ -4555,16 +4989,19 @@
       <c r="G143" s="3"/>
       <c r="H143" s="4"/>
       <c r="I143" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="J143" s="7">
+        <v>142.0</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
       <c r="A144" s="3"/>
       <c r="B144" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D144" s="3"/>
       <c r="E144" s="4"/>
@@ -4574,16 +5011,19 @@
       <c r="G144" s="3"/>
       <c r="H144" s="4"/>
       <c r="I144" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J144" s="7">
+        <v>143.0</v>
       </c>
     </row>
     <row r="145" ht="14.25" customHeight="1">
       <c r="A145" s="3"/>
       <c r="B145" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D145" s="3"/>
       <c r="E145" s="4"/>
@@ -4593,16 +5033,19 @@
       <c r="G145" s="3"/>
       <c r="H145" s="4"/>
       <c r="I145" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J145" s="7">
+        <v>144.0</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
       <c r="A146" s="3"/>
       <c r="B146" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D146" s="3"/>
       <c r="E146" s="4"/>
@@ -4612,16 +5055,19 @@
       <c r="G146" s="3"/>
       <c r="H146" s="4"/>
       <c r="I146" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="J146" s="7">
+        <v>145.0</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
       <c r="A147" s="3"/>
       <c r="B147" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D147" s="3"/>
       <c r="E147" s="4"/>
@@ -4631,16 +5077,19 @@
       <c r="G147" s="3"/>
       <c r="H147" s="4"/>
       <c r="I147" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J147" s="7">
+        <v>146.0</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
       <c r="A148" s="3"/>
       <c r="B148" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D148" s="3"/>
       <c r="E148" s="4"/>
@@ -4650,16 +5099,19 @@
       <c r="G148" s="3"/>
       <c r="H148" s="4"/>
       <c r="I148" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
+      </c>
+      <c r="J148" s="7">
+        <v>147.0</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
       <c r="A149" s="3"/>
       <c r="B149" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D149" s="3"/>
       <c r="E149" s="4"/>
@@ -4669,16 +5121,19 @@
       <c r="G149" s="3"/>
       <c r="H149" s="4"/>
       <c r="I149" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
+      </c>
+      <c r="J149" s="7">
+        <v>148.0</v>
       </c>
     </row>
     <row r="150" ht="14.25" customHeight="1">
       <c r="A150" s="3"/>
       <c r="B150" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D150" s="3"/>
       <c r="E150" s="4"/>
@@ -4688,16 +5143,19 @@
       <c r="G150" s="3"/>
       <c r="H150" s="4"/>
       <c r="I150" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
+      </c>
+      <c r="J150" s="7">
+        <v>149.0</v>
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
       <c r="A151" s="3"/>
       <c r="B151" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D151" s="3"/>
       <c r="E151" s="4"/>
@@ -4707,16 +5165,19 @@
       <c r="G151" s="3"/>
       <c r="H151" s="4"/>
       <c r="I151" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
+      </c>
+      <c r="J151" s="7">
+        <v>150.0</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
       <c r="A152" s="3"/>
       <c r="B152" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D152" s="3"/>
       <c r="E152" s="4"/>
@@ -4726,16 +5187,19 @@
       <c r="G152" s="3"/>
       <c r="H152" s="4"/>
       <c r="I152" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J152" s="7">
+        <v>151.0</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
       <c r="A153" s="3"/>
       <c r="B153" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D153" s="3"/>
       <c r="E153" s="4"/>
@@ -4745,16 +5209,19 @@
       <c r="G153" s="3"/>
       <c r="H153" s="4"/>
       <c r="I153" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J153" s="7">
+        <v>152.0</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
       <c r="A154" s="3"/>
       <c r="B154" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D154" s="3"/>
       <c r="E154" s="4"/>
@@ -4764,16 +5231,19 @@
       <c r="G154" s="3"/>
       <c r="H154" s="4"/>
       <c r="I154" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
+      </c>
+      <c r="J154" s="7">
+        <v>153.0</v>
       </c>
     </row>
     <row r="155" ht="14.25" customHeight="1">
       <c r="A155" s="3"/>
       <c r="B155" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D155" s="3"/>
       <c r="E155" s="4"/>
@@ -4783,16 +5253,19 @@
       <c r="G155" s="3"/>
       <c r="H155" s="4"/>
       <c r="I155" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J155" s="7">
+        <v>154.0</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
       <c r="A156" s="3"/>
       <c r="B156" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D156" s="3"/>
       <c r="E156" s="4"/>
@@ -4802,16 +5275,19 @@
       <c r="G156" s="3"/>
       <c r="H156" s="4"/>
       <c r="I156" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J156" s="7">
+        <v>155.0</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
       <c r="A157" s="3"/>
       <c r="B157" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D157" s="3"/>
       <c r="E157" s="4"/>
@@ -4821,16 +5297,19 @@
       <c r="G157" s="3"/>
       <c r="H157" s="4"/>
       <c r="I157" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J157" s="7">
+        <v>156.0</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
       <c r="A158" s="3"/>
       <c r="B158" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D158" s="3"/>
       <c r="E158" s="4"/>
@@ -4840,16 +5319,19 @@
       <c r="G158" s="3"/>
       <c r="H158" s="4"/>
       <c r="I158" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J158" s="7">
+        <v>157.0</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
       <c r="A159" s="3"/>
       <c r="B159" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D159" s="3"/>
       <c r="E159" s="4"/>
@@ -4859,16 +5341,19 @@
       <c r="G159" s="3"/>
       <c r="H159" s="4"/>
       <c r="I159" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J159" s="7">
+        <v>158.0</v>
       </c>
     </row>
     <row r="160" ht="14.25" customHeight="1">
       <c r="A160" s="3"/>
       <c r="B160" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="C160" s="4" t="s">
         <v>296</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>295</v>
       </c>
       <c r="D160" s="3"/>
       <c r="E160" s="4"/>
@@ -4878,16 +5363,19 @@
       <c r="G160" s="3"/>
       <c r="H160" s="4"/>
       <c r="I160" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J160" s="7">
+        <v>159.0</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
       <c r="A161" s="3"/>
       <c r="B161" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D161" s="3"/>
       <c r="E161" s="4"/>
@@ -4897,16 +5385,19 @@
       <c r="G161" s="3"/>
       <c r="H161" s="4"/>
       <c r="I161" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J161" s="7">
+        <v>160.0</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
       <c r="A162" s="3"/>
       <c r="B162" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="C162" s="4" t="s">
         <v>299</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>298</v>
       </c>
       <c r="D162" s="3"/>
       <c r="E162" s="4"/>
@@ -4916,16 +5407,19 @@
       <c r="G162" s="3"/>
       <c r="H162" s="4"/>
       <c r="I162" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J162" s="7">
+        <v>161.0</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
       <c r="A163" s="3"/>
       <c r="B163" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D163" s="3"/>
       <c r="E163" s="4"/>
@@ -4935,16 +5429,19 @@
       <c r="G163" s="3"/>
       <c r="H163" s="4"/>
       <c r="I163" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
+      </c>
+      <c r="J163" s="7">
+        <v>162.0</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
       <c r="A164" s="3"/>
       <c r="B164" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D164" s="3"/>
       <c r="E164" s="4"/>
@@ -4954,16 +5451,19 @@
       <c r="G164" s="3"/>
       <c r="H164" s="4"/>
       <c r="I164" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J164" s="7">
+        <v>163.0</v>
       </c>
     </row>
     <row r="165" ht="14.25" customHeight="1">
       <c r="A165" s="3"/>
       <c r="B165" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D165" s="3"/>
       <c r="E165" s="4"/>
@@ -4973,16 +5473,19 @@
       <c r="G165" s="3"/>
       <c r="H165" s="4"/>
       <c r="I165" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="J165" s="7">
+        <v>164.0</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
       <c r="A166" s="3"/>
       <c r="B166" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D166" s="3"/>
       <c r="E166" s="4"/>
@@ -4992,16 +5495,19 @@
       <c r="G166" s="3"/>
       <c r="H166" s="4"/>
       <c r="I166" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J166" s="7">
+        <v>165.0</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
       <c r="A167" s="3"/>
       <c r="B167" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D167" s="3"/>
       <c r="E167" s="4"/>
@@ -5011,16 +5517,19 @@
       <c r="G167" s="3"/>
       <c r="H167" s="4"/>
       <c r="I167" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J167" s="7">
+        <v>166.0</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
       <c r="A168" s="3"/>
       <c r="B168" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D168" s="3"/>
       <c r="E168" s="4"/>
@@ -5030,16 +5539,19 @@
       <c r="G168" s="3"/>
       <c r="H168" s="4"/>
       <c r="I168" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J168" s="7">
+        <v>167.0</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
       <c r="A169" s="3"/>
       <c r="B169" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D169" s="3"/>
       <c r="E169" s="4"/>
@@ -5049,16 +5561,19 @@
       <c r="G169" s="3"/>
       <c r="H169" s="4"/>
       <c r="I169" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J169" s="7">
+        <v>168.0</v>
       </c>
     </row>
     <row r="170" ht="14.25" customHeight="1">
       <c r="A170" s="3"/>
       <c r="B170" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C170" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="C170" s="4" t="s">
-        <v>310</v>
       </c>
       <c r="D170" s="3"/>
       <c r="E170" s="4"/>
@@ -5068,16 +5583,19 @@
       <c r="G170" s="3"/>
       <c r="H170" s="4"/>
       <c r="I170" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J170" s="7">
+        <v>169.0</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
       <c r="A171" s="3"/>
       <c r="B171" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D171" s="3"/>
       <c r="E171" s="4"/>
@@ -5087,16 +5605,19 @@
       <c r="G171" s="3"/>
       <c r="H171" s="4"/>
       <c r="I171" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J171" s="7">
+        <v>170.0</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
       <c r="A172" s="3"/>
       <c r="B172" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D172" s="3"/>
       <c r="E172" s="4"/>
@@ -5106,16 +5627,19 @@
       <c r="G172" s="3"/>
       <c r="H172" s="4"/>
       <c r="I172" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J172" s="7">
+        <v>171.0</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
       <c r="A173" s="3"/>
       <c r="B173" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D173" s="3"/>
       <c r="E173" s="4"/>
@@ -5125,16 +5649,19 @@
       <c r="G173" s="3"/>
       <c r="H173" s="4"/>
       <c r="I173" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J173" s="7">
+        <v>172.0</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
       <c r="A174" s="3"/>
       <c r="B174" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D174" s="3"/>
       <c r="E174" s="4"/>
@@ -5144,16 +5671,19 @@
       <c r="G174" s="3"/>
       <c r="H174" s="4"/>
       <c r="I174" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J174" s="7">
+        <v>173.0</v>
       </c>
     </row>
     <row r="175" ht="14.25" customHeight="1">
       <c r="A175" s="3"/>
       <c r="B175" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D175" s="3"/>
       <c r="E175" s="4"/>
@@ -5163,16 +5693,19 @@
       <c r="G175" s="3"/>
       <c r="H175" s="4"/>
       <c r="I175" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J175" s="7">
+        <v>174.0</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
       <c r="A176" s="3"/>
       <c r="B176" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D176" s="3"/>
       <c r="E176" s="4"/>
@@ -5182,16 +5715,19 @@
       <c r="G176" s="3"/>
       <c r="H176" s="4"/>
       <c r="I176" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J176" s="7">
+        <v>175.0</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
       <c r="A177" s="3"/>
       <c r="B177" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D177" s="3"/>
       <c r="E177" s="4"/>
@@ -5201,16 +5737,19 @@
       <c r="G177" s="3"/>
       <c r="H177" s="4"/>
       <c r="I177" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J177" s="7">
+        <v>176.0</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
       <c r="A178" s="3"/>
       <c r="B178" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D178" s="3"/>
       <c r="E178" s="4"/>
@@ -5220,16 +5759,19 @@
       <c r="G178" s="3"/>
       <c r="H178" s="4"/>
       <c r="I178" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J178" s="7">
+        <v>177.0</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
       <c r="A179" s="3"/>
       <c r="B179" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D179" s="3"/>
       <c r="E179" s="4"/>
@@ -5239,16 +5781,19 @@
       <c r="G179" s="3"/>
       <c r="H179" s="4"/>
       <c r="I179" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J179" s="7">
+        <v>178.0</v>
       </c>
     </row>
     <row r="180" ht="14.25" customHeight="1">
       <c r="A180" s="3"/>
       <c r="B180" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D180" s="3"/>
       <c r="E180" s="4"/>
@@ -5258,16 +5803,19 @@
       <c r="G180" s="3"/>
       <c r="H180" s="4"/>
       <c r="I180" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J180" s="7">
+        <v>179.0</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
       <c r="A181" s="3"/>
       <c r="B181" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D181" s="3"/>
       <c r="E181" s="4"/>
@@ -5277,16 +5825,19 @@
       <c r="G181" s="3"/>
       <c r="H181" s="4"/>
       <c r="I181" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="J181" s="7">
+        <v>180.0</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
       <c r="A182" s="3"/>
       <c r="B182" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D182" s="3"/>
       <c r="E182" s="4"/>
@@ -5296,16 +5847,19 @@
       <c r="G182" s="3"/>
       <c r="H182" s="4"/>
       <c r="I182" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
+      </c>
+      <c r="J182" s="7">
+        <v>181.0</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
       <c r="A183" s="3"/>
       <c r="B183" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D183" s="3"/>
       <c r="E183" s="4"/>
@@ -5315,16 +5869,19 @@
       <c r="G183" s="3"/>
       <c r="H183" s="4"/>
       <c r="I183" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
+      </c>
+      <c r="J183" s="7">
+        <v>182.0</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
       <c r="A184" s="3"/>
       <c r="B184" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D184" s="3"/>
       <c r="E184" s="4"/>
@@ -5334,16 +5891,19 @@
       <c r="G184" s="3"/>
       <c r="H184" s="4"/>
       <c r="I184" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J184" s="7">
+        <v>183.0</v>
       </c>
     </row>
     <row r="185" ht="14.25" customHeight="1">
       <c r="A185" s="3"/>
       <c r="B185" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D185" s="3"/>
       <c r="E185" s="4"/>
@@ -5353,16 +5913,19 @@
       <c r="G185" s="3"/>
       <c r="H185" s="4"/>
       <c r="I185" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J185" s="7">
+        <v>184.0</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
       <c r="A186" s="3"/>
       <c r="B186" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D186" s="3"/>
       <c r="E186" s="4"/>
@@ -5372,16 +5935,19 @@
       <c r="G186" s="3"/>
       <c r="H186" s="4"/>
       <c r="I186" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J186" s="7">
+        <v>185.0</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
       <c r="A187" s="3"/>
       <c r="B187" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D187" s="3"/>
       <c r="E187" s="4"/>
@@ -5391,16 +5957,19 @@
       <c r="G187" s="3"/>
       <c r="H187" s="4"/>
       <c r="I187" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J187" s="7">
+        <v>186.0</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
       <c r="A188" s="3"/>
       <c r="B188" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D188" s="3"/>
       <c r="E188" s="4"/>
@@ -5410,16 +5979,19 @@
       <c r="G188" s="3"/>
       <c r="H188" s="4"/>
       <c r="I188" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J188" s="7">
+        <v>187.0</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
       <c r="A189" s="3"/>
       <c r="B189" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C189" s="4" t="s">
         <v>347</v>
-      </c>
-      <c r="C189" s="4" t="s">
-        <v>346</v>
       </c>
       <c r="D189" s="3"/>
       <c r="E189" s="4"/>
@@ -5429,16 +6001,19 @@
       <c r="G189" s="3"/>
       <c r="H189" s="4"/>
       <c r="I189" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J189" s="7">
+        <v>188.0</v>
       </c>
     </row>
     <row r="190" ht="14.25" customHeight="1">
       <c r="A190" s="3"/>
       <c r="B190" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D190" s="3"/>
       <c r="E190" s="4"/>
@@ -5448,16 +6023,19 @@
       <c r="G190" s="3"/>
       <c r="H190" s="4"/>
       <c r="I190" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J190" s="7">
+        <v>189.0</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
       <c r="A191" s="3"/>
       <c r="B191" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D191" s="3"/>
       <c r="E191" s="4"/>
@@ -5467,16 +6045,19 @@
       <c r="G191" s="3"/>
       <c r="H191" s="4"/>
       <c r="I191" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J191" s="7">
+        <v>190.0</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
       <c r="A192" s="3"/>
       <c r="B192" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D192" s="3"/>
       <c r="E192" s="4"/>
@@ -5486,16 +6067,19 @@
       <c r="G192" s="3"/>
       <c r="H192" s="4"/>
       <c r="I192" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J192" s="7">
+        <v>191.0</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
       <c r="A193" s="3"/>
       <c r="B193" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D193" s="3"/>
       <c r="E193" s="4"/>
@@ -5505,16 +6089,19 @@
       <c r="G193" s="3"/>
       <c r="H193" s="4"/>
       <c r="I193" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J193" s="7">
+        <v>192.0</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
       <c r="A194" s="3"/>
       <c r="B194" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D194" s="3"/>
       <c r="E194" s="4"/>
@@ -5524,16 +6111,19 @@
       <c r="G194" s="3"/>
       <c r="H194" s="4"/>
       <c r="I194" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
+      </c>
+      <c r="J194" s="7">
+        <v>193.0</v>
       </c>
     </row>
     <row r="195" ht="14.25" customHeight="1">
       <c r="A195" s="3"/>
       <c r="B195" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D195" s="3"/>
       <c r="E195" s="4"/>
@@ -5543,16 +6133,19 @@
       <c r="G195" s="3"/>
       <c r="H195" s="4"/>
       <c r="I195" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
+      </c>
+      <c r="J195" s="7">
+        <v>194.0</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
       <c r="A196" s="3"/>
       <c r="B196" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D196" s="3"/>
       <c r="E196" s="4"/>
@@ -5562,16 +6155,19 @@
       <c r="G196" s="3"/>
       <c r="H196" s="4"/>
       <c r="I196" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J196" s="7">
+        <v>195.0</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
       <c r="A197" s="3"/>
       <c r="B197" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D197" s="3"/>
       <c r="E197" s="4"/>
@@ -5581,16 +6177,19 @@
       <c r="G197" s="3"/>
       <c r="H197" s="4"/>
       <c r="I197" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="J197" s="7">
+        <v>196.0</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
       <c r="A198" s="3"/>
       <c r="B198" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D198" s="3"/>
       <c r="E198" s="4"/>
@@ -5600,16 +6199,19 @@
       <c r="G198" s="3"/>
       <c r="H198" s="4"/>
       <c r="I198" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
+      </c>
+      <c r="J198" s="7">
+        <v>197.0</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
       <c r="A199" s="3"/>
       <c r="B199" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D199" s="3"/>
       <c r="E199" s="4"/>
@@ -5619,16 +6221,19 @@
       <c r="G199" s="3"/>
       <c r="H199" s="4"/>
       <c r="I199" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J199" s="7">
+        <v>198.0</v>
       </c>
     </row>
     <row r="200" ht="14.25" customHeight="1">
       <c r="A200" s="3"/>
       <c r="B200" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D200" s="3"/>
       <c r="E200" s="4"/>
@@ -5638,16 +6243,19 @@
       <c r="G200" s="3"/>
       <c r="H200" s="4"/>
       <c r="I200" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J200" s="7">
+        <v>199.0</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
       <c r="A201" s="3"/>
       <c r="B201" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D201" s="3"/>
       <c r="E201" s="4"/>
@@ -5657,16 +6265,19 @@
       <c r="G201" s="3"/>
       <c r="H201" s="4"/>
       <c r="I201" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J201" s="7">
+        <v>200.0</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
       <c r="A202" s="3"/>
       <c r="B202" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C202" s="4" t="s">
         <v>370</v>
-      </c>
-      <c r="C202" s="4" t="s">
-        <v>369</v>
       </c>
       <c r="D202" s="3"/>
       <c r="E202" s="4"/>
@@ -5676,16 +6287,19 @@
       <c r="G202" s="3"/>
       <c r="H202" s="4"/>
       <c r="I202" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J202" s="7">
+        <v>201.0</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
       <c r="A203" s="3"/>
       <c r="B203" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D203" s="3"/>
       <c r="E203" s="4"/>
@@ -5695,16 +6309,19 @@
       <c r="G203" s="3"/>
       <c r="H203" s="4"/>
       <c r="I203" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J203" s="7">
+        <v>202.0</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
       <c r="A204" s="3"/>
       <c r="B204" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D204" s="3"/>
       <c r="E204" s="4"/>
@@ -5714,16 +6331,19 @@
       <c r="G204" s="3"/>
       <c r="H204" s="4"/>
       <c r="I204" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
+      </c>
+      <c r="J204" s="7">
+        <v>203.0</v>
       </c>
     </row>
     <row r="205" ht="14.25" customHeight="1">
       <c r="A205" s="3"/>
       <c r="B205" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D205" s="3"/>
       <c r="E205" s="4"/>
@@ -5733,16 +6353,19 @@
       <c r="G205" s="3"/>
       <c r="H205" s="4"/>
       <c r="I205" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J205" s="7">
+        <v>204.0</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
       <c r="A206" s="3"/>
       <c r="B206" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D206" s="3"/>
       <c r="E206" s="4"/>
@@ -5752,16 +6375,19 @@
       <c r="G206" s="3"/>
       <c r="H206" s="4"/>
       <c r="I206" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J206" s="7">
+        <v>205.0</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
       <c r="A207" s="3"/>
       <c r="B207" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D207" s="3"/>
       <c r="E207" s="4"/>
@@ -5771,16 +6397,19 @@
       <c r="G207" s="3"/>
       <c r="H207" s="4"/>
       <c r="I207" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J207" s="7">
+        <v>206.0</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
       <c r="A208" s="3"/>
       <c r="B208" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D208" s="3"/>
       <c r="E208" s="4"/>
@@ -5790,16 +6419,19 @@
       <c r="G208" s="3"/>
       <c r="H208" s="4"/>
       <c r="I208" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J208" s="7">
+        <v>207.0</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
       <c r="A209" s="3"/>
       <c r="B209" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D209" s="3"/>
       <c r="E209" s="4"/>
@@ -5809,16 +6441,19 @@
       <c r="G209" s="3"/>
       <c r="H209" s="4"/>
       <c r="I209" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J209" s="7">
+        <v>208.0</v>
       </c>
     </row>
     <row r="210" ht="14.25" customHeight="1">
       <c r="A210" s="3"/>
       <c r="B210" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C210" s="4" t="s">
         <v>384</v>
-      </c>
-      <c r="C210" s="4" t="s">
-        <v>383</v>
       </c>
       <c r="D210" s="3"/>
       <c r="E210" s="4"/>
@@ -5828,16 +6463,19 @@
       <c r="G210" s="3"/>
       <c r="H210" s="4"/>
       <c r="I210" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J210" s="7">
+        <v>209.0</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
       <c r="A211" s="3"/>
       <c r="B211" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D211" s="3"/>
       <c r="E211" s="4"/>
@@ -5847,16 +6485,19 @@
       <c r="G211" s="3"/>
       <c r="H211" s="4"/>
       <c r="I211" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J211" s="7">
+        <v>210.0</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
       <c r="A212" s="3"/>
       <c r="B212" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D212" s="3"/>
       <c r="E212" s="4"/>
@@ -5866,16 +6507,19 @@
       <c r="G212" s="3"/>
       <c r="H212" s="4"/>
       <c r="I212" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J212" s="7">
+        <v>211.0</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
       <c r="A213" s="3"/>
       <c r="B213" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D213" s="3"/>
       <c r="E213" s="4"/>
@@ -5885,16 +6529,19 @@
       <c r="G213" s="3"/>
       <c r="H213" s="4"/>
       <c r="I213" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J213" s="7">
+        <v>212.0</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
       <c r="A214" s="3"/>
       <c r="B214" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D214" s="3"/>
       <c r="E214" s="4"/>
@@ -5904,16 +6551,19 @@
       <c r="G214" s="3"/>
       <c r="H214" s="4"/>
       <c r="I214" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J214" s="7">
+        <v>213.0</v>
       </c>
     </row>
     <row r="215" ht="14.25" customHeight="1">
       <c r="A215" s="3"/>
       <c r="B215" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D215" s="3"/>
       <c r="E215" s="4"/>
@@ -5923,16 +6573,19 @@
       <c r="G215" s="3"/>
       <c r="H215" s="4"/>
       <c r="I215" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J215" s="7">
+        <v>214.0</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
       <c r="A216" s="3"/>
       <c r="B216" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D216" s="3"/>
       <c r="E216" s="4"/>
@@ -5942,16 +6595,19 @@
       <c r="G216" s="3"/>
       <c r="H216" s="4"/>
       <c r="I216" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J216" s="7">
+        <v>215.0</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
       <c r="A217" s="3"/>
       <c r="B217" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C217" s="4" t="s">
         <v>396</v>
-      </c>
-      <c r="C217" s="4" t="s">
-        <v>395</v>
       </c>
       <c r="D217" s="3"/>
       <c r="E217" s="4"/>
@@ -5961,16 +6617,19 @@
       <c r="G217" s="3"/>
       <c r="H217" s="4"/>
       <c r="I217" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J217" s="7">
+        <v>216.0</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
       <c r="A218" s="3"/>
       <c r="B218" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D218" s="3"/>
       <c r="E218" s="4"/>
@@ -5980,16 +6639,19 @@
       <c r="G218" s="3"/>
       <c r="H218" s="4"/>
       <c r="I218" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
+      </c>
+      <c r="J218" s="7">
+        <v>217.0</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
       <c r="A219" s="3"/>
       <c r="B219" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D219" s="3"/>
       <c r="E219" s="4"/>
@@ -5999,16 +6661,19 @@
       <c r="G219" s="3"/>
       <c r="H219" s="4"/>
       <c r="I219" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="J219" s="7">
+        <v>218.0</v>
       </c>
     </row>
     <row r="220" ht="14.25" customHeight="1">
       <c r="A220" s="3"/>
       <c r="B220" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C220" s="4" t="s">
         <v>401</v>
-      </c>
-      <c r="C220" s="4" t="s">
-        <v>400</v>
       </c>
       <c r="D220" s="3"/>
       <c r="E220" s="4"/>
@@ -6018,16 +6683,19 @@
       <c r="G220" s="3"/>
       <c r="H220" s="4"/>
       <c r="I220" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="J220" s="7">
+        <v>219.0</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
       <c r="A221" s="3"/>
       <c r="B221" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D221" s="3"/>
       <c r="E221" s="4"/>
@@ -6037,16 +6705,19 @@
       <c r="G221" s="3"/>
       <c r="H221" s="4"/>
       <c r="I221" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J221" s="7">
+        <v>220.0</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
       <c r="A222" s="3"/>
       <c r="B222" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D222" s="3"/>
       <c r="E222" s="4"/>
@@ -6056,16 +6727,19 @@
       <c r="G222" s="3"/>
       <c r="H222" s="4"/>
       <c r="I222" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="J222" s="7">
+        <v>221.0</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
       <c r="A223" s="3"/>
       <c r="B223" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D223" s="3"/>
       <c r="E223" s="4"/>
@@ -6075,16 +6749,19 @@
       <c r="G223" s="3"/>
       <c r="H223" s="4"/>
       <c r="I223" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J223" s="7">
+        <v>222.0</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
       <c r="A224" s="3"/>
       <c r="B224" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D224" s="3"/>
       <c r="E224" s="4"/>
@@ -6094,16 +6771,19 @@
       <c r="G224" s="3"/>
       <c r="H224" s="4"/>
       <c r="I224" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J224" s="7">
+        <v>223.0</v>
       </c>
     </row>
     <row r="225" ht="14.25" customHeight="1">
       <c r="A225" s="3"/>
       <c r="B225" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D225" s="3"/>
       <c r="E225" s="4"/>
@@ -6113,16 +6793,19 @@
       <c r="G225" s="3"/>
       <c r="H225" s="4"/>
       <c r="I225" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
+      </c>
+      <c r="J225" s="7">
+        <v>224.0</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
       <c r="A226" s="3"/>
       <c r="B226" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D226" s="3"/>
       <c r="E226" s="4"/>
@@ -6132,16 +6815,19 @@
       <c r="G226" s="3"/>
       <c r="H226" s="4"/>
       <c r="I226" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="J226" s="7">
+        <v>225.0</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
       <c r="A227" s="3"/>
       <c r="B227" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D227" s="3"/>
       <c r="E227" s="4"/>
@@ -6151,16 +6837,19 @@
       <c r="G227" s="3"/>
       <c r="H227" s="4"/>
       <c r="I227" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J227" s="7">
+        <v>226.0</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
       <c r="A228" s="3"/>
       <c r="B228" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C228" s="4" t="s">
         <v>417</v>
-      </c>
-      <c r="C228" s="4" t="s">
-        <v>416</v>
       </c>
       <c r="D228" s="3"/>
       <c r="E228" s="4"/>
@@ -6170,16 +6859,19 @@
       <c r="G228" s="3"/>
       <c r="H228" s="4"/>
       <c r="I228" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J228" s="7">
+        <v>227.0</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
       <c r="A229" s="3"/>
       <c r="B229" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D229" s="3"/>
       <c r="E229" s="4"/>
@@ -6189,16 +6881,19 @@
       <c r="G229" s="3"/>
       <c r="H229" s="4"/>
       <c r="I229" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J229" s="7">
+        <v>228.0</v>
       </c>
     </row>
     <row r="230" ht="14.25" customHeight="1">
       <c r="A230" s="3"/>
       <c r="B230" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="C230" s="4" t="s">
         <v>420</v>
-      </c>
-      <c r="C230" s="4" t="s">
-        <v>419</v>
       </c>
       <c r="D230" s="3"/>
       <c r="E230" s="4"/>
@@ -6208,16 +6903,19 @@
       <c r="G230" s="3"/>
       <c r="H230" s="4"/>
       <c r="I230" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J230" s="7">
+        <v>229.0</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
       <c r="A231" s="3"/>
       <c r="B231" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D231" s="3"/>
       <c r="E231" s="4"/>
@@ -6227,16 +6925,19 @@
       <c r="G231" s="3"/>
       <c r="H231" s="4"/>
       <c r="I231" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J231" s="7">
+        <v>230.0</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
       <c r="A232" s="3"/>
       <c r="B232" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D232" s="3"/>
       <c r="E232" s="4"/>
@@ -6246,16 +6947,19 @@
       <c r="G232" s="3"/>
       <c r="H232" s="4"/>
       <c r="I232" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
+      </c>
+      <c r="J232" s="7">
+        <v>231.0</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
       <c r="A233" s="3"/>
       <c r="B233" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D233" s="3"/>
       <c r="E233" s="4"/>
@@ -6265,16 +6969,19 @@
       <c r="G233" s="3"/>
       <c r="H233" s="4"/>
       <c r="I233" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J233" s="7">
+        <v>232.0</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
       <c r="A234" s="3"/>
       <c r="B234" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D234" s="3"/>
       <c r="E234" s="4"/>
@@ -6284,16 +6991,19 @@
       <c r="G234" s="3"/>
       <c r="H234" s="4"/>
       <c r="I234" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J234" s="7">
+        <v>233.0</v>
       </c>
     </row>
     <row r="235" ht="14.25" customHeight="1">
       <c r="A235" s="3"/>
       <c r="B235" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D235" s="3"/>
       <c r="E235" s="4"/>
@@ -6303,16 +7013,19 @@
       <c r="G235" s="3"/>
       <c r="H235" s="4"/>
       <c r="I235" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J235" s="7">
+        <v>234.0</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
       <c r="A236" s="3"/>
       <c r="B236" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D236" s="3"/>
       <c r="E236" s="4"/>
@@ -6322,16 +7035,19 @@
       <c r="G236" s="3"/>
       <c r="H236" s="4"/>
       <c r="I236" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J236" s="7">
+        <v>235.0</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
       <c r="A237" s="3"/>
       <c r="B237" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C237" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D237" s="3"/>
       <c r="E237" s="4"/>
@@ -6341,16 +7057,19 @@
       <c r="G237" s="3"/>
       <c r="H237" s="4"/>
       <c r="I237" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J237" s="7">
+        <v>236.0</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
       <c r="A238" s="3"/>
       <c r="B238" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D238" s="3"/>
       <c r="E238" s="4"/>
@@ -6360,16 +7079,19 @@
       <c r="G238" s="3"/>
       <c r="H238" s="4"/>
       <c r="I238" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J238" s="7">
+        <v>237.0</v>
       </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
       <c r="A239" s="3"/>
       <c r="B239" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C239" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D239" s="3"/>
       <c r="E239" s="4"/>
@@ -6379,16 +7101,19 @@
       <c r="G239" s="3"/>
       <c r="H239" s="4"/>
       <c r="I239" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J239" s="7">
+        <v>238.0</v>
       </c>
     </row>
     <row r="240" ht="14.25" customHeight="1">
       <c r="A240" s="3"/>
       <c r="B240" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D240" s="3"/>
       <c r="E240" s="4"/>
@@ -6398,16 +7123,19 @@
       <c r="G240" s="3"/>
       <c r="H240" s="4"/>
       <c r="I240" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J240" s="7">
+        <v>239.0</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
       <c r="A241" s="3"/>
       <c r="B241" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D241" s="3"/>
       <c r="E241" s="4"/>
@@ -6417,16 +7145,19 @@
       <c r="G241" s="3"/>
       <c r="H241" s="4"/>
       <c r="I241" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J241" s="7">
+        <v>240.0</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
       <c r="A242" s="3"/>
       <c r="B242" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D242" s="3"/>
       <c r="E242" s="4"/>
@@ -6436,16 +7167,19 @@
       <c r="G242" s="3"/>
       <c r="H242" s="4"/>
       <c r="I242" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J242" s="7">
+        <v>241.0</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
       <c r="A243" s="3"/>
       <c r="B243" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C243" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D243" s="3"/>
       <c r="E243" s="4"/>
@@ -6455,16 +7189,19 @@
       <c r="G243" s="3"/>
       <c r="H243" s="4"/>
       <c r="I243" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J243" s="7">
+        <v>242.0</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
       <c r="A244" s="3"/>
       <c r="B244" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D244" s="3"/>
       <c r="E244" s="4"/>
@@ -6474,16 +7211,19 @@
       <c r="G244" s="3"/>
       <c r="H244" s="4"/>
       <c r="I244" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J244" s="7">
+        <v>243.0</v>
       </c>
     </row>
     <row r="245" ht="14.25" customHeight="1">
       <c r="A245" s="3"/>
       <c r="B245" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C245" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D245" s="3"/>
       <c r="E245" s="4"/>
@@ -6493,16 +7233,19 @@
       <c r="G245" s="3"/>
       <c r="H245" s="4"/>
       <c r="I245" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
+      </c>
+      <c r="J245" s="7">
+        <v>244.0</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
       <c r="A246" s="3"/>
       <c r="B246" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C246" s="4" t="s">
         <v>443</v>
-      </c>
-      <c r="C246" s="4" t="s">
-        <v>442</v>
       </c>
       <c r="D246" s="3"/>
       <c r="E246" s="4"/>
@@ -6512,16 +7255,19 @@
       <c r="G246" s="3"/>
       <c r="H246" s="4"/>
       <c r="I246" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
+      </c>
+      <c r="J246" s="7">
+        <v>245.0</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
       <c r="A247" s="3"/>
       <c r="B247" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C247" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D247" s="3"/>
       <c r="E247" s="4"/>
@@ -6531,16 +7277,19 @@
       <c r="G247" s="3"/>
       <c r="H247" s="4"/>
       <c r="I247" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
+      </c>
+      <c r="J247" s="7">
+        <v>246.0</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
       <c r="A248" s="3"/>
       <c r="B248" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D248" s="3"/>
       <c r="E248" s="4"/>
@@ -6550,16 +7299,19 @@
       <c r="G248" s="3"/>
       <c r="H248" s="4"/>
       <c r="I248" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J248" s="7">
+        <v>247.0</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
       <c r="A249" s="3"/>
       <c r="B249" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C249" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D249" s="3"/>
       <c r="E249" s="4"/>
@@ -6569,16 +7321,19 @@
       <c r="G249" s="3"/>
       <c r="H249" s="4"/>
       <c r="I249" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J249" s="7">
+        <v>248.0</v>
       </c>
     </row>
     <row r="250" ht="14.25" customHeight="1">
       <c r="A250" s="3"/>
       <c r="B250" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D250" s="3"/>
       <c r="E250" s="4"/>
@@ -6588,16 +7343,19 @@
       <c r="G250" s="3"/>
       <c r="H250" s="4"/>
       <c r="I250" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J250" s="7">
+        <v>249.0</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
       <c r="A251" s="3"/>
       <c r="B251" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D251" s="3"/>
       <c r="E251" s="4"/>
@@ -6607,16 +7365,19 @@
       <c r="G251" s="3"/>
       <c r="H251" s="4"/>
       <c r="I251" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J251" s="7">
+        <v>250.0</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
       <c r="A252" s="3"/>
       <c r="B252" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D252" s="3"/>
       <c r="E252" s="4"/>
@@ -6626,16 +7387,19 @@
       <c r="G252" s="3"/>
       <c r="H252" s="4"/>
       <c r="I252" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J252" s="7">
+        <v>251.0</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
       <c r="A253" s="3"/>
       <c r="B253" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C253" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D253" s="3"/>
       <c r="E253" s="4"/>
@@ -6645,16 +7409,19 @@
       <c r="G253" s="3"/>
       <c r="H253" s="4"/>
       <c r="I253" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J253" s="7">
+        <v>252.0</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
       <c r="A254" s="3"/>
       <c r="B254" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D254" s="3"/>
       <c r="E254" s="4"/>
@@ -6664,16 +7431,19 @@
       <c r="G254" s="3"/>
       <c r="H254" s="4"/>
       <c r="I254" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J254" s="7">
+        <v>253.0</v>
       </c>
     </row>
     <row r="255" ht="14.25" customHeight="1">
       <c r="A255" s="3"/>
       <c r="B255" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C255" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D255" s="3"/>
       <c r="E255" s="4"/>
@@ -6683,16 +7453,19 @@
       <c r="G255" s="3"/>
       <c r="H255" s="4"/>
       <c r="I255" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J255" s="7">
+        <v>254.0</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
       <c r="A256" s="3"/>
       <c r="B256" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D256" s="3"/>
       <c r="E256" s="4"/>
@@ -6702,16 +7475,19 @@
       <c r="G256" s="3"/>
       <c r="H256" s="4"/>
       <c r="I256" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J256" s="7">
+        <v>255.0</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
       <c r="A257" s="3"/>
       <c r="B257" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C257" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D257" s="3"/>
       <c r="E257" s="4"/>
@@ -6721,16 +7497,19 @@
       <c r="G257" s="3"/>
       <c r="H257" s="4"/>
       <c r="I257" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J257" s="7">
+        <v>256.0</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
       <c r="A258" s="3"/>
       <c r="B258" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D258" s="3"/>
       <c r="E258" s="4"/>
@@ -6740,7 +7519,10 @@
       <c r="G258" s="3"/>
       <c r="H258" s="4"/>
       <c r="I258" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J258" s="7">
+        <v>257.0</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1"/>
@@ -7518,79 +8300,79 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
